--- a/resources/sample_model.xlsx
+++ b/resources/sample_model.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Capcs 1\PycharmProjects\pythonProject3\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home_\PycharmProjects\excel-to-excel\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3D0EC0-30CE-484D-B1EB-EC0ECE65721C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lot x" sheetId="3" r:id="rId1"/>
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -69,6 +70,21 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">Ofertant: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Achiziţia nu a avut loc</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>lot</t>
+  </si>
+  <si>
+    <t>https://achizitii.md/ro/public/tender/21487715/</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -119,26 +135,11 @@
       <t>Model:</t>
     </r>
   </si>
-  <si>
-    <t xml:space="preserve">Ofertant: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Achiziţia nu a avut loc</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>lot</t>
-  </si>
-  <si>
-    <t>https://achizitii.md/ro/public/tender/21487715/</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;L&quot;"/>
     <numFmt numFmtId="165" formatCode="0.00000%"/>
@@ -616,6 +617,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -658,15 +660,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Акцент5 2" xfId="2"/>
-    <cellStyle name="Акцент5 2 2" xfId="3"/>
+    <cellStyle name="Акцент5 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Акцент5 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Гиперссылка" xfId="5" builtinId="8"/>
-    <cellStyle name="Гиперссылка 2" xfId="4"/>
+    <cellStyle name="Гиперссылка 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1260,70 +1261,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G108"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="3" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="33" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" style="34" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" style="35" customWidth="1"/>
-    <col min="5" max="6" width="50.7109375" style="36" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="3"/>
+    <col min="3" max="3" width="25.44140625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" style="35" customWidth="1"/>
+    <col min="5" max="5" width="50.77734375" style="36" customWidth="1"/>
+    <col min="6" max="6" width="50.6640625" style="36" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="48"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
       <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+    <row r="5" spans="1:6" ht="21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="39"/>
@@ -1334,8 +1336,8 @@
       <c r="E5" s="11"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:6" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+    <row r="6" spans="1:6" ht="21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="52"/>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
       <c r="D6" s="10" t="s">
@@ -1344,8 +1346,8 @@
       <c r="E6" s="12"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="52"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13" t="s">
         <v>5</v>
@@ -1360,8 +1362,8 @@
       </c>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="52"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17" t="s">
         <v>6</v>
@@ -1372,8 +1374,8 @@
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="53"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -1385,7 +1387,7 @@
       </c>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
       <c r="C10" s="24"/>
@@ -1393,15 +1395,15 @@
       <c r="E10" s="26"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:6" ht="162.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="162.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="55"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
     </row>
-    <row r="12" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -1409,7 +1411,7 @@
       <c r="E12" s="29"/>
       <c r="F12" s="28"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -1417,7 +1419,7 @@
       <c r="E13" s="29"/>
       <c r="F13" s="28"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="27"/>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -1425,7 +1427,7 @@
       <c r="E14" s="29"/>
       <c r="F14" s="31"/>
     </row>
-    <row r="15" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27"/>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -1433,7 +1435,7 @@
       <c r="E15" s="29"/>
       <c r="F15" s="31"/>
     </row>
-    <row r="16" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -1443,7 +1445,7 @@
       <c r="E16" s="29"/>
       <c r="F16" s="31"/>
     </row>
-    <row r="17" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="27"/>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -1451,7 +1453,7 @@
       <c r="E17" s="29"/>
       <c r="F17" s="31"/>
     </row>
-    <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27"/>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
@@ -1459,7 +1461,7 @@
       <c r="E18" s="29"/>
       <c r="F18" s="31"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="27"/>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
@@ -1467,7 +1469,7 @@
       <c r="E19" s="29"/>
       <c r="F19" s="31"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27"/>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -1475,7 +1477,7 @@
       <c r="E20" s="29"/>
       <c r="F20" s="31"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="27"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -1483,7 +1485,7 @@
       <c r="E21" s="29"/>
       <c r="F21" s="31"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="27"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -1491,7 +1493,7 @@
       <c r="E22" s="29"/>
       <c r="F22" s="31"/>
     </row>
-    <row r="23" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -1499,7 +1501,7 @@
       <c r="E23" s="29"/>
       <c r="F23" s="31"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="27"/>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -1507,7 +1509,7 @@
       <c r="E24" s="29"/>
       <c r="F24" s="31"/>
     </row>
-    <row r="25" spans="1:6" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="165" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27"/>
       <c r="B25" s="29"/>
       <c r="C25" s="29"/>
@@ -1515,7 +1517,7 @@
       <c r="E25" s="29"/>
       <c r="F25" s="31"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="27"/>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -1523,7 +1525,7 @@
       <c r="E26" s="29"/>
       <c r="F26" s="31"/>
     </row>
-    <row r="27" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27"/>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -1531,7 +1533,7 @@
       <c r="E27" s="29"/>
       <c r="F27" s="31"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="27"/>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
@@ -1539,7 +1541,7 @@
       <c r="E28" s="29"/>
       <c r="F28" s="31"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="27"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -1547,7 +1549,7 @@
       <c r="E29" s="29"/>
       <c r="F29" s="31"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
@@ -1555,7 +1557,7 @@
       <c r="E30" s="29"/>
       <c r="F30" s="31"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="27"/>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -1563,7 +1565,7 @@
       <c r="E31" s="29"/>
       <c r="F31" s="31"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="27"/>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -1571,7 +1573,7 @@
       <c r="E32" s="29"/>
       <c r="F32" s="31"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="27"/>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -1579,7 +1581,7 @@
       <c r="E33" s="29"/>
       <c r="F33" s="31"/>
     </row>
-    <row r="34" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="27"/>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
@@ -1587,7 +1589,7 @@
       <c r="E34" s="29"/>
       <c r="F34" s="31"/>
     </row>
-    <row r="35" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="27"/>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
@@ -1595,7 +1597,7 @@
       <c r="E35" s="29"/>
       <c r="F35" s="31"/>
     </row>
-    <row r="36" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="27"/>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -1608,7 +1610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="27"/>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -1616,7 +1618,7 @@
       <c r="E37" s="29"/>
       <c r="F37" s="31"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="27"/>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
@@ -1624,7 +1626,7 @@
       <c r="E38" s="29"/>
       <c r="F38" s="31"/>
     </row>
-    <row r="39" spans="1:7" ht="291" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="291" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="27"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29"/>
@@ -1632,7 +1634,7 @@
       <c r="E39" s="29"/>
       <c r="F39" s="31"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="27"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -1640,7 +1642,7 @@
       <c r="E40" s="29"/>
       <c r="F40" s="31"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="27"/>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -1648,7 +1650,7 @@
       <c r="E41" s="29"/>
       <c r="F41" s="31"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="27"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -1656,7 +1658,7 @@
       <c r="E42" s="29"/>
       <c r="F42" s="31"/>
     </row>
-    <row r="43" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="27"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -1664,7 +1666,7 @@
       <c r="E43" s="29"/>
       <c r="F43" s="31"/>
     </row>
-    <row r="44" spans="1:7" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="131.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="27"/>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
@@ -1672,7 +1674,7 @@
       <c r="E44" s="29"/>
       <c r="F44" s="31"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="27"/>
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
@@ -1680,7 +1682,7 @@
       <c r="E45" s="29"/>
       <c r="F45" s="31"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="27"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -1688,7 +1690,7 @@
       <c r="E46" s="29"/>
       <c r="F46" s="31"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="27"/>
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
@@ -1696,7 +1698,7 @@
       <c r="E47" s="29"/>
       <c r="F47" s="31"/>
     </row>
-    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="27"/>
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
@@ -1704,7 +1706,7 @@
       <c r="E48" s="29"/>
       <c r="F48" s="31"/>
     </row>
-    <row r="49" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="27"/>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -1712,7 +1714,7 @@
       <c r="E49" s="29"/>
       <c r="F49" s="31"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="27"/>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
@@ -1720,7 +1722,7 @@
       <c r="E50" s="29"/>
       <c r="F50" s="31"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="27"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
@@ -1728,7 +1730,7 @@
       <c r="E51" s="29"/>
       <c r="F51" s="31"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="27"/>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -1736,7 +1738,7 @@
       <c r="E52" s="29"/>
       <c r="F52" s="31"/>
     </row>
-    <row r="53" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="27"/>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
@@ -1744,7 +1746,7 @@
       <c r="E53" s="29"/>
       <c r="F53" s="31"/>
     </row>
-    <row r="54" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="27"/>
       <c r="B54" s="29"/>
       <c r="C54" s="29"/>
@@ -1752,7 +1754,7 @@
       <c r="E54" s="29"/>
       <c r="F54" s="31"/>
     </row>
-    <row r="55" spans="1:6" s="6" customFormat="1" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" s="6" customFormat="1" ht="152.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="27"/>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -1760,17 +1762,17 @@
       <c r="E55" s="29"/>
       <c r="F55" s="31"/>
     </row>
-    <row r="56" spans="1:6" s="6" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" s="6" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="27"/>
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
       <c r="D56" s="37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="31"/>
     </row>
-    <row r="57" spans="1:6" s="6" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" s="6" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="27"/>
       <c r="B57" s="29"/>
       <c r="C57" s="29"/>
@@ -1778,7 +1780,7 @@
       <c r="E57" s="29"/>
       <c r="F57" s="31"/>
     </row>
-    <row r="58" spans="1:6" s="6" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" s="6" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="27"/>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -1786,7 +1788,7 @@
       <c r="E58" s="29"/>
       <c r="F58" s="31"/>
     </row>
-    <row r="59" spans="1:6" s="6" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" s="6" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="27"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
@@ -1794,7 +1796,7 @@
       <c r="E59" s="29"/>
       <c r="F59" s="31"/>
     </row>
-    <row r="60" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="27"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29"/>
@@ -1802,7 +1804,7 @@
       <c r="E60" s="29"/>
       <c r="F60" s="31"/>
     </row>
-    <row r="61" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="27"/>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -1810,7 +1812,7 @@
       <c r="E61" s="29"/>
       <c r="F61" s="31"/>
     </row>
-    <row r="62" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" s="6" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="27"/>
       <c r="B62" s="29"/>
       <c r="C62" s="29"/>
@@ -1818,7 +1820,7 @@
       <c r="E62" s="29"/>
       <c r="F62" s="31"/>
     </row>
-    <row r="63" spans="1:6" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="27"/>
       <c r="B63" s="29"/>
       <c r="C63" s="29"/>
@@ -1826,7 +1828,7 @@
       <c r="E63" s="29"/>
       <c r="F63" s="31"/>
     </row>
-    <row r="64" spans="1:6" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="27"/>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -1834,7 +1836,7 @@
       <c r="E64" s="29"/>
       <c r="F64" s="31"/>
     </row>
-    <row r="65" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="27"/>
       <c r="B65" s="29"/>
       <c r="C65" s="29"/>
@@ -1842,7 +1844,7 @@
       <c r="E65" s="29"/>
       <c r="F65" s="31"/>
     </row>
-    <row r="66" spans="1:6" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="27"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29"/>
@@ -1850,7 +1852,7 @@
       <c r="E66" s="29"/>
       <c r="F66" s="31"/>
     </row>
-    <row r="67" spans="1:6" s="6" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" s="6" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="27"/>
       <c r="B67" s="29"/>
       <c r="C67" s="29"/>
@@ -1858,7 +1860,7 @@
       <c r="E67" s="29"/>
       <c r="F67" s="31"/>
     </row>
-    <row r="68" spans="1:6" s="6" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" s="6" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="27"/>
       <c r="B68" s="29"/>
       <c r="C68" s="29"/>
@@ -1866,7 +1868,7 @@
       <c r="E68" s="29"/>
       <c r="F68" s="31"/>
     </row>
-    <row r="69" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="27"/>
       <c r="B69" s="29"/>
       <c r="C69" s="29"/>
@@ -1874,7 +1876,7 @@
       <c r="E69" s="29"/>
       <c r="F69" s="31"/>
     </row>
-    <row r="70" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="27"/>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -1882,7 +1884,7 @@
       <c r="E70" s="29"/>
       <c r="F70" s="31"/>
     </row>
-    <row r="71" spans="1:6" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="27"/>
       <c r="B71" s="29"/>
       <c r="C71" s="29"/>
@@ -1890,7 +1892,7 @@
       <c r="E71" s="29"/>
       <c r="F71" s="31"/>
     </row>
-    <row r="72" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="27"/>
       <c r="B72" s="29"/>
       <c r="C72" s="29"/>
@@ -1898,7 +1900,7 @@
       <c r="E72" s="29"/>
       <c r="F72" s="31"/>
     </row>
-    <row r="73" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="27"/>
       <c r="B73" s="29"/>
       <c r="C73" s="29"/>
@@ -1906,7 +1908,7 @@
       <c r="E73" s="29"/>
       <c r="F73" s="31"/>
     </row>
-    <row r="74" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="27"/>
       <c r="B74" s="29"/>
       <c r="C74" s="29"/>
@@ -1914,7 +1916,7 @@
       <c r="E74" s="29"/>
       <c r="F74" s="31"/>
     </row>
-    <row r="75" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="27"/>
       <c r="B75" s="29"/>
       <c r="C75" s="29"/>
@@ -1922,7 +1924,7 @@
       <c r="E75" s="29"/>
       <c r="F75" s="31"/>
     </row>
-    <row r="76" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="29"/>
       <c r="C76" s="29"/>
@@ -1930,7 +1932,7 @@
       <c r="E76" s="29"/>
       <c r="F76" s="31"/>
     </row>
-    <row r="77" spans="1:6" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="29"/>
       <c r="C77" s="29"/>
@@ -1938,7 +1940,7 @@
       <c r="E77" s="29"/>
       <c r="F77" s="31"/>
     </row>
-    <row r="78" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="27"/>
       <c r="B78" s="29"/>
       <c r="C78" s="29"/>
@@ -1946,7 +1948,7 @@
       <c r="E78" s="29"/>
       <c r="F78" s="31"/>
     </row>
-    <row r="79" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="27"/>
       <c r="B79" s="29"/>
       <c r="C79" s="29"/>
@@ -1954,7 +1956,7 @@
       <c r="E79" s="29"/>
       <c r="F79" s="31"/>
     </row>
-    <row r="80" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="27"/>
       <c r="B80" s="29"/>
       <c r="C80" s="29"/>
@@ -1962,7 +1964,7 @@
       <c r="E80" s="29"/>
       <c r="F80" s="31"/>
     </row>
-    <row r="81" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="27"/>
       <c r="B81" s="29"/>
       <c r="C81" s="29"/>
@@ -1970,7 +1972,7 @@
       <c r="E81" s="29"/>
       <c r="F81" s="31"/>
     </row>
-    <row r="82" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="B82" s="29"/>
       <c r="C82" s="29"/>
@@ -1978,7 +1980,7 @@
       <c r="E82" s="29"/>
       <c r="F82" s="31"/>
     </row>
-    <row r="83" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="27"/>
       <c r="B83" s="29"/>
       <c r="C83" s="29"/>
@@ -1986,7 +1988,7 @@
       <c r="E83" s="29"/>
       <c r="F83" s="31"/>
     </row>
-    <row r="84" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="27"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29"/>
@@ -1994,7 +1996,7 @@
       <c r="E84" s="29"/>
       <c r="F84" s="31"/>
     </row>
-    <row r="85" spans="1:7" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="27"/>
       <c r="B85" s="29"/>
       <c r="C85" s="29"/>
@@ -2002,7 +2004,7 @@
       <c r="E85" s="29"/>
       <c r="F85" s="31"/>
     </row>
-    <row r="86" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="27"/>
       <c r="B86" s="29"/>
       <c r="C86" s="29"/>
@@ -2010,7 +2012,7 @@
       <c r="E86" s="29"/>
       <c r="F86" s="31"/>
     </row>
-    <row r="87" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="27"/>
       <c r="B87" s="29"/>
       <c r="C87" s="29"/>
@@ -2018,7 +2020,7 @@
       <c r="E87" s="29"/>
       <c r="F87" s="31"/>
     </row>
-    <row r="88" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="32"/>
       <c r="B88" s="29"/>
       <c r="C88" s="29"/>
@@ -2026,7 +2028,7 @@
       <c r="E88" s="29"/>
       <c r="F88" s="31"/>
     </row>
-    <row r="89" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="32"/>
       <c r="B89" s="29"/>
       <c r="C89" s="29"/>
@@ -2034,7 +2036,7 @@
       <c r="E89" s="29"/>
       <c r="F89" s="31"/>
     </row>
-    <row r="90" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="32"/>
       <c r="B90" s="29"/>
       <c r="C90" s="29"/>
@@ -2042,7 +2044,7 @@
       <c r="E90" s="29"/>
       <c r="F90" s="31"/>
     </row>
-    <row r="91" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="32"/>
       <c r="B91" s="29"/>
       <c r="C91" s="29"/>
@@ -2051,7 +2053,7 @@
       <c r="F91" s="31"/>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="32"/>
       <c r="B92" s="29"/>
       <c r="C92" s="29"/>
@@ -2060,7 +2062,7 @@
       <c r="F92" s="31"/>
       <c r="G92" s="6"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="32"/>
       <c r="B93" s="29"/>
       <c r="C93" s="29"/>
@@ -2069,7 +2071,7 @@
       <c r="F93" s="31"/>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="32"/>
       <c r="B94" s="29"/>
       <c r="C94" s="29"/>
@@ -2078,7 +2080,7 @@
       <c r="F94" s="31"/>
       <c r="G94" s="6"/>
     </row>
-    <row r="95" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="32"/>
       <c r="B95" s="29"/>
       <c r="C95" s="29"/>
@@ -2087,7 +2089,7 @@
       <c r="F95" s="31"/>
       <c r="G95" s="6"/>
     </row>
-    <row r="96" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="32"/>
       <c r="B96" s="29"/>
       <c r="C96" s="29"/>
@@ -2096,7 +2098,7 @@
       <c r="F96" s="31"/>
       <c r="G96" s="6"/>
     </row>
-    <row r="97" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="32"/>
       <c r="B97" s="29"/>
       <c r="C97" s="29"/>
@@ -2105,7 +2107,7 @@
       <c r="F97" s="31"/>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="32"/>
       <c r="B98" s="29"/>
       <c r="C98" s="29"/>
@@ -2114,7 +2116,7 @@
       <c r="F98" s="31"/>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="32"/>
       <c r="B99" s="29"/>
       <c r="C99" s="29"/>
@@ -2127,7 +2129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="32"/>
       <c r="B100" s="29"/>
       <c r="C100" s="29"/>
@@ -2136,7 +2138,7 @@
       <c r="F100" s="31"/>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="1:7" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="108.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
       <c r="B101" s="29"/>
       <c r="C101" s="29"/>
@@ -2145,7 +2147,7 @@
       <c r="F101" s="31"/>
       <c r="G101" s="6"/>
     </row>
-    <row r="102" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="32"/>
       <c r="B102" s="29"/>
       <c r="C102" s="29"/>
@@ -2154,7 +2156,7 @@
       <c r="F102" s="31"/>
       <c r="G102" s="6"/>
     </row>
-    <row r="103" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="32"/>
       <c r="B103" s="29"/>
       <c r="C103" s="29"/>
@@ -2163,7 +2165,7 @@
       <c r="F103" s="31"/>
       <c r="G103" s="6"/>
     </row>
-    <row r="104" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="32"/>
       <c r="B104" s="29"/>
       <c r="C104" s="29"/>
@@ -2172,7 +2174,7 @@
       <c r="F104" s="31"/>
       <c r="G104" s="6"/>
     </row>
-    <row r="105" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="32"/>
       <c r="B105" s="29"/>
       <c r="C105" s="29"/>
@@ -2181,7 +2183,7 @@
       <c r="F105" s="31"/>
       <c r="G105" s="6"/>
     </row>
-    <row r="106" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="32"/>
       <c r="B106" s="29"/>
       <c r="C106" s="29"/>
@@ -2190,7 +2192,7 @@
       <c r="F106" s="31"/>
       <c r="G106" s="6"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="32"/>
       <c r="B107" s="29"/>
       <c r="C107" s="29"/>
@@ -2199,7 +2201,7 @@
       <c r="F107" s="31"/>
       <c r="G107" s="6"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="32"/>
       <c r="B108" s="29"/>
       <c r="C108" s="29"/>
@@ -2215,7 +2217,7 @@
     <mergeCell ref="B11:D11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -2225,9 +2227,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
